--- a/샘플_배당.xlsx
+++ b/샘플_배당.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="배당내역" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006366F1"/>
-        <bgColor rgb="006366F1"/>
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,31 +60,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,21 +472,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>소유자</t>
@@ -513,7 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>아빠</t>
@@ -539,7 +559,7 @@
           <t>005930</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
@@ -549,16 +569,16 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>36100</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2분기 정기배당</t>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2분기 정기 배당</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>아빠</t>
@@ -584,7 +604,7 @@
           <t>QQQM</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Invesco NASDAQ 100 ETF</t>
         </is>
@@ -594,16 +614,16 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>45.5</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>분기 배당 입금</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>엄마</t>
@@ -629,7 +649,7 @@
           <t>000660</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
@@ -639,55 +659,100 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>중간배당</t>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>중간 배당</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>엄마</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>미래에셋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>미래에셋ISA</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>379810</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>KODEX 미국나스닥100</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>분기 분배금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>자녀</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>토스증권</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>토스자녀계좌</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Schwab US Dividend Equity ETF</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>28.3</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>분기 배당 입금</t>
         </is>
